--- a/Task3.xlsx
+++ b/Task3.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
   <si>
     <t>Threads</t>
   </si>
@@ -67,6 +67,14 @@
   </si>
   <si>
     <t>LOCK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+3223190</t>
+  </si>
+  <si>
+    <t>23765232
+23765232</t>
   </si>
 </sst>
 </file>
@@ -578,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -590,22 +598,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
@@ -618,12 +616,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -653,6 +645,25 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -957,49 +968,49 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="F4" s="63"/>
+      <c r="G4" s="63"/>
     </row>
     <row r="5" spans="2:13" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="6" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="15" t="s">
+      <c r="B6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="25" t="s">
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="21" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="25" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -1014,608 +1025,608 @@
       <c r="H7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="26"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="35">
+      <c r="B8" s="29">
         <v>2</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="30">
-        <v>118</v>
+      <c r="D8" s="26">
+        <v>160</v>
       </c>
       <c r="E8" s="4">
-        <v>131</v>
+        <v>206</v>
       </c>
       <c r="F8" s="4">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="G8" s="4">
-        <v>216</v>
-      </c>
-      <c r="H8" s="21">
-        <v>95</v>
-      </c>
-      <c r="I8" s="27">
+        <v>98</v>
+      </c>
+      <c r="H8" s="17">
+        <v>184</v>
+      </c>
+      <c r="I8" s="23">
         <f>AVERAGE(D8:H8)</f>
-        <v>134.19999999999999</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="44"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="46">
-        <v>2879765</v>
+      <c r="B9" s="38"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="40">
+        <v>3013644</v>
       </c>
       <c r="E9" s="8">
-        <v>2758430</v>
+        <v>3033131</v>
       </c>
       <c r="F9" s="8">
-        <v>2561198</v>
+        <v>2954189</v>
       </c>
       <c r="G9" s="8">
-        <v>2983418</v>
-      </c>
-      <c r="H9" s="47">
-        <v>2526083</v>
-      </c>
-      <c r="I9" s="48">
+        <v>2425192</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="42">
         <f t="shared" ref="I9:I36" si="0">AVERAGE(D9:H9)</f>
-        <v>2741778.8</v>
+        <v>2856539</v>
       </c>
     </row>
     <row r="10" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="60"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="23"/>
     </row>
     <row r="11" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="49">
+      <c r="B11" s="43">
         <v>2</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="51">
-        <v>107</v>
-      </c>
-      <c r="E11" s="43">
-        <v>92</v>
-      </c>
-      <c r="F11" s="43">
-        <v>108</v>
-      </c>
-      <c r="G11" s="43">
-        <v>77</v>
-      </c>
-      <c r="H11" s="52">
-        <v>111</v>
-      </c>
-      <c r="I11" s="53">
-        <f t="shared" si="0"/>
-        <v>99</v>
+      <c r="D11" s="45">
+        <v>129</v>
+      </c>
+      <c r="E11" s="37">
+        <v>119</v>
+      </c>
+      <c r="F11" s="37">
+        <v>123</v>
+      </c>
+      <c r="G11" s="37">
+        <v>119</v>
+      </c>
+      <c r="H11" s="46">
+        <v>175</v>
+      </c>
+      <c r="I11" s="47">
+        <f t="shared" si="0"/>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="17"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="31">
-        <v>2063286</v>
+      <c r="B12" s="14"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="27">
+        <v>2015928</v>
       </c>
       <c r="E12" s="3">
-        <v>2054155</v>
+        <v>2025168</v>
       </c>
       <c r="F12" s="3">
-        <v>2069998</v>
+        <v>2021820</v>
       </c>
       <c r="G12" s="3">
-        <v>2000523</v>
-      </c>
-      <c r="H12" s="23">
-        <v>2102774</v>
-      </c>
-      <c r="I12" s="27">
-        <f t="shared" si="0"/>
-        <v>2058147.2</v>
+        <v>2016050</v>
+      </c>
+      <c r="H12" s="19">
+        <v>2009653</v>
+      </c>
+      <c r="I12" s="23">
+        <f t="shared" si="0"/>
+        <v>2017723.8</v>
       </c>
     </row>
     <row r="13" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="17"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="31"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="27"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="27"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="23"/>
     </row>
     <row r="14" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="16">
+      <c r="B14" s="13">
         <v>4</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="30">
-        <v>537</v>
+      <c r="D14" s="26">
+        <v>688</v>
       </c>
       <c r="E14" s="4">
-        <v>535</v>
+        <v>616</v>
       </c>
       <c r="F14" s="4">
-        <v>525</v>
+        <v>627</v>
       </c>
       <c r="G14" s="4">
-        <v>416</v>
-      </c>
-      <c r="H14" s="22">
-        <v>481</v>
-      </c>
-      <c r="I14" s="27">
-        <f t="shared" si="0"/>
-        <v>498.8</v>
-      </c>
-      <c r="M14" s="14"/>
+        <v>524</v>
+      </c>
+      <c r="H14" s="18">
+        <v>436</v>
+      </c>
+      <c r="I14" s="23">
+        <f t="shared" si="0"/>
+        <v>578.20000000000005</v>
+      </c>
+      <c r="M14" s="12"/>
     </row>
     <row r="15" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="44"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="46">
-        <v>9732019</v>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40">
+        <v>10724919</v>
       </c>
       <c r="E15" s="8">
-        <v>9177202</v>
+        <v>7733428</v>
       </c>
       <c r="F15" s="8">
-        <v>9764220</v>
+        <v>7029419</v>
       </c>
       <c r="G15" s="8">
-        <v>10330689</v>
-      </c>
-      <c r="H15" s="47">
-        <v>10626332</v>
-      </c>
-      <c r="I15" s="48">
-        <f t="shared" si="0"/>
-        <v>9926092.4000000004</v>
+        <v>9274223</v>
+      </c>
+      <c r="H15" s="41">
+        <v>8521116</v>
+      </c>
+      <c r="I15" s="42">
+        <f t="shared" si="0"/>
+        <v>8656621</v>
       </c>
     </row>
     <row r="16" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="60"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="27"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="23"/>
     </row>
     <row r="17" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="49">
+      <c r="B17" s="43">
         <v>4</v>
       </c>
-      <c r="C17" s="50" t="s">
+      <c r="C17" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="51">
-        <v>491</v>
-      </c>
-      <c r="E17" s="43">
-        <v>429</v>
-      </c>
-      <c r="F17" s="43">
-        <v>578</v>
-      </c>
-      <c r="G17" s="43">
-        <v>559</v>
-      </c>
-      <c r="H17" s="52">
-        <v>613</v>
-      </c>
-      <c r="I17" s="53">
-        <f t="shared" si="0"/>
-        <v>534</v>
+      <c r="D17" s="45">
+        <v>432</v>
+      </c>
+      <c r="E17" s="37">
+        <v>470</v>
+      </c>
+      <c r="F17" s="37">
+        <v>316</v>
+      </c>
+      <c r="G17" s="37">
+        <v>611</v>
+      </c>
+      <c r="H17" s="46">
+        <v>483</v>
+      </c>
+      <c r="I17" s="47">
+        <f t="shared" si="0"/>
+        <v>462.4</v>
       </c>
     </row>
     <row r="18" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="56">
-        <v>4861980</v>
+      <c r="B18" s="48"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="50">
+        <v>4288674</v>
       </c>
       <c r="E18" s="7">
-        <v>5017683</v>
+        <v>4167163</v>
       </c>
       <c r="F18" s="7">
-        <v>5106572</v>
+        <v>4162649</v>
       </c>
       <c r="G18" s="7">
-        <v>5023726</v>
-      </c>
-      <c r="H18" s="57">
-        <v>5138061</v>
-      </c>
-      <c r="I18" s="48">
-        <f t="shared" si="0"/>
-        <v>5029604.4000000004</v>
+        <v>4268492</v>
+      </c>
+      <c r="H18" s="51">
+        <v>4202048</v>
+      </c>
+      <c r="I18" s="42">
+        <f t="shared" si="0"/>
+        <v>4217805.2</v>
       </c>
     </row>
     <row r="19" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="62"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="27"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="53"/>
+      <c r="H19" s="53"/>
+      <c r="I19" s="23"/>
     </row>
     <row r="20" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="35">
+      <c r="B20" s="29">
         <v>8</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="58">
-        <v>1171</v>
+      <c r="D20" s="52">
+        <v>2280</v>
       </c>
       <c r="E20" s="10">
-        <v>1561</v>
+        <v>2355</v>
       </c>
       <c r="F20" s="10">
-        <v>1629</v>
+        <v>1739</v>
       </c>
       <c r="G20" s="10">
-        <v>1338</v>
-      </c>
-      <c r="H20" s="21">
-        <v>1455</v>
-      </c>
-      <c r="I20" s="53">
-        <f t="shared" si="0"/>
-        <v>1430.8</v>
+        <v>1842</v>
+      </c>
+      <c r="H20" s="17">
+        <v>2015</v>
+      </c>
+      <c r="I20" s="47">
+        <f t="shared" si="0"/>
+        <v>2046.2</v>
       </c>
     </row>
     <row r="21" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="44"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="46">
-        <v>21836867</v>
+      <c r="B21" s="38"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="40">
+        <v>29073011</v>
       </c>
       <c r="E21" s="8">
-        <v>27221495</v>
+        <v>27244584</v>
       </c>
       <c r="F21" s="8">
-        <v>29755323</v>
+        <v>30432960</v>
       </c>
       <c r="G21" s="8">
-        <v>33177398</v>
-      </c>
-      <c r="H21" s="47">
-        <v>37178724</v>
-      </c>
-      <c r="I21" s="48">
-        <f t="shared" si="0"/>
-        <v>29833961.399999999</v>
+        <v>23052519</v>
+      </c>
+      <c r="H21" s="64" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="42">
+        <f t="shared" si="0"/>
+        <v>27450768.5</v>
       </c>
     </row>
     <row r="22" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="60"/>
-      <c r="C22" s="61"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="27"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="23"/>
     </row>
     <row r="23" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="49">
+      <c r="B23" s="43">
         <v>8</v>
       </c>
-      <c r="C23" s="50" t="s">
+      <c r="C23" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="51">
-        <v>1787</v>
-      </c>
-      <c r="E23" s="43">
-        <v>1463</v>
-      </c>
-      <c r="F23" s="43">
-        <v>1880</v>
-      </c>
-      <c r="G23" s="43">
-        <v>2250</v>
-      </c>
-      <c r="H23" s="52">
-        <v>2031</v>
-      </c>
-      <c r="I23" s="53">
-        <f t="shared" si="0"/>
-        <v>1882.2</v>
+      <c r="D23" s="45">
+        <v>1233</v>
+      </c>
+      <c r="E23" s="37">
+        <v>1500</v>
+      </c>
+      <c r="F23" s="37">
+        <v>2281</v>
+      </c>
+      <c r="G23" s="37">
+        <v>1822</v>
+      </c>
+      <c r="H23" s="46">
+        <v>2140</v>
+      </c>
+      <c r="I23" s="47">
+        <f t="shared" si="0"/>
+        <v>1795.2</v>
       </c>
     </row>
     <row r="24" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="54"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="56">
-        <v>10193496</v>
+      <c r="B24" s="48"/>
+      <c r="C24" s="49"/>
+      <c r="D24" s="50">
+        <v>8709783</v>
       </c>
       <c r="E24" s="7">
-        <v>10597276</v>
+        <v>8745542</v>
       </c>
       <c r="F24" s="7">
-        <v>10487150</v>
+        <v>8910226</v>
       </c>
       <c r="G24" s="7">
-        <v>10800519</v>
-      </c>
-      <c r="H24" s="57">
-        <v>11559756</v>
-      </c>
-      <c r="I24" s="48">
-        <f t="shared" si="0"/>
-        <v>10727639.4</v>
+        <v>10164954</v>
+      </c>
+      <c r="H24" s="51">
+        <v>9132874</v>
+      </c>
+      <c r="I24" s="42">
+        <f t="shared" si="0"/>
+        <v>9132675.8000000007</v>
       </c>
     </row>
     <row r="25" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="62"/>
-      <c r="C25" s="63"/>
-      <c r="D25" s="59"/>
-      <c r="E25" s="59"/>
-      <c r="F25" s="59"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="27"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="53"/>
+      <c r="E25" s="53"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="53"/>
+      <c r="H25" s="53"/>
+      <c r="I25" s="23"/>
     </row>
     <row r="26" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="35">
+      <c r="B26" s="29">
         <v>16</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="58">
-        <v>4400</v>
+      <c r="D26" s="52">
+        <v>6054</v>
       </c>
       <c r="E26" s="10">
-        <v>4752</v>
+        <v>6201</v>
       </c>
       <c r="F26" s="10">
-        <v>6408</v>
+        <v>6630</v>
       </c>
       <c r="G26" s="10">
-        <v>6347</v>
-      </c>
-      <c r="H26" s="21">
-        <v>5614</v>
-      </c>
-      <c r="I26" s="53">
-        <f t="shared" si="0"/>
-        <v>5504.2</v>
+        <v>7697</v>
+      </c>
+      <c r="H26" s="17">
+        <v>6273</v>
+      </c>
+      <c r="I26" s="47">
+        <f t="shared" si="0"/>
+        <v>6571</v>
       </c>
     </row>
     <row r="27" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="44"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="46">
-        <v>74583480</v>
+      <c r="B27" s="38"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="40">
+        <v>74444287</v>
       </c>
       <c r="E27" s="8">
-        <v>101658264</v>
+        <v>106281970</v>
       </c>
       <c r="F27" s="8">
-        <v>132908773</v>
+        <v>121554377</v>
       </c>
       <c r="G27" s="8">
-        <v>95751567</v>
-      </c>
-      <c r="H27" s="47">
+        <v>97810478</v>
+      </c>
+      <c r="H27" s="41">
         <v>81107249</v>
       </c>
-      <c r="I27" s="48">
-        <f t="shared" si="0"/>
-        <v>97201866.599999994</v>
+      <c r="I27" s="42">
+        <f t="shared" si="0"/>
+        <v>96239672.200000003</v>
       </c>
     </row>
     <row r="28" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="60"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="42"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="42"/>
-      <c r="G28" s="42"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="27"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="23"/>
     </row>
     <row r="29" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="49">
+      <c r="B29" s="43">
         <v>16</v>
       </c>
-      <c r="C29" s="50" t="s">
+      <c r="C29" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="51">
-        <v>5283</v>
-      </c>
-      <c r="E29" s="43">
-        <v>6594</v>
-      </c>
-      <c r="F29" s="43">
-        <v>6776</v>
-      </c>
-      <c r="G29" s="43">
-        <v>6130</v>
-      </c>
-      <c r="H29" s="52">
-        <v>6286</v>
-      </c>
-      <c r="I29" s="53">
-        <f t="shared" si="0"/>
-        <v>6213.8</v>
+      <c r="D29" s="45">
+        <v>5446</v>
+      </c>
+      <c r="E29" s="37">
+        <v>5241</v>
+      </c>
+      <c r="F29" s="37">
+        <v>5410</v>
+      </c>
+      <c r="G29" s="37">
+        <v>6629</v>
+      </c>
+      <c r="H29" s="46">
+        <v>9822</v>
+      </c>
+      <c r="I29" s="47">
+        <f t="shared" si="0"/>
+        <v>6509.6</v>
       </c>
     </row>
     <row r="30" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="54"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="56">
-        <v>22616980</v>
+      <c r="B30" s="48"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="50">
+        <v>19049520</v>
       </c>
       <c r="E30" s="7">
-        <v>20835000</v>
+        <v>18060635</v>
       </c>
       <c r="F30" s="7">
-        <v>21089070</v>
+        <v>19243755</v>
       </c>
       <c r="G30" s="7">
-        <v>20441441</v>
-      </c>
-      <c r="H30" s="57">
-        <v>19746192</v>
-      </c>
-      <c r="I30" s="48">
-        <f t="shared" si="0"/>
-        <v>20945736.600000001</v>
+        <v>19554301</v>
+      </c>
+      <c r="H30" s="51">
+        <v>22787666</v>
+      </c>
+      <c r="I30" s="42">
+        <f t="shared" si="0"/>
+        <v>19739175.399999999</v>
       </c>
     </row>
     <row r="31" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="62"/>
-      <c r="C31" s="63"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="59"/>
-      <c r="F31" s="59"/>
-      <c r="G31" s="59"/>
-      <c r="H31" s="59"/>
-      <c r="I31" s="27"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="53"/>
+      <c r="H31" s="53"/>
+      <c r="I31" s="23"/>
     </row>
     <row r="32" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="35">
+      <c r="B32" s="29">
         <v>32</v>
       </c>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D32" s="51">
-        <v>21060</v>
-      </c>
-      <c r="E32" s="43">
-        <v>23017</v>
-      </c>
-      <c r="F32" s="43">
-        <v>26062</v>
-      </c>
-      <c r="G32" s="43">
-        <v>25857</v>
-      </c>
-      <c r="H32" s="52">
-        <v>25678</v>
-      </c>
-      <c r="I32" s="53">
-        <f t="shared" si="0"/>
-        <v>24334.799999999999</v>
+      <c r="D32" s="52">
+        <v>21387</v>
+      </c>
+      <c r="E32" s="10">
+        <v>28833</v>
+      </c>
+      <c r="F32" s="10">
+        <v>43800</v>
+      </c>
+      <c r="G32" s="10">
+        <v>32889</v>
+      </c>
+      <c r="H32" s="17">
+        <v>40206</v>
+      </c>
+      <c r="I32" s="47">
+        <f t="shared" si="0"/>
+        <v>33423</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="44"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="56">
-        <v>404994307</v>
-      </c>
-      <c r="E33" s="7">
-        <v>307845962</v>
-      </c>
-      <c r="F33" s="7">
-        <v>347747561</v>
-      </c>
-      <c r="G33" s="7">
-        <v>365080671</v>
-      </c>
-      <c r="H33" s="57">
-        <v>381790461</v>
-      </c>
-      <c r="I33" s="48">
-        <f t="shared" si="0"/>
-        <v>361491792.39999998</v>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="40">
+        <v>374156605</v>
+      </c>
+      <c r="E33" s="8">
+        <v>400245655</v>
+      </c>
+      <c r="F33" s="8">
+        <v>411841211</v>
+      </c>
+      <c r="G33" s="8">
+        <v>358964408</v>
+      </c>
+      <c r="H33" s="41">
+        <v>360398381</v>
+      </c>
+      <c r="I33" s="42">
+        <f t="shared" si="0"/>
+        <v>381121252</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="60"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="27"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="49">
+      <c r="B35" s="43">
         <v>32</v>
       </c>
-      <c r="C35" s="50" t="s">
+      <c r="C35" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="51">
-        <v>20154</v>
-      </c>
-      <c r="E35" s="43">
-        <v>21152</v>
-      </c>
-      <c r="F35" s="43">
-        <v>24890</v>
-      </c>
-      <c r="G35" s="43">
-        <v>21811</v>
-      </c>
-      <c r="H35" s="52">
-        <v>19119</v>
-      </c>
-      <c r="I35" s="53">
-        <f t="shared" si="0"/>
-        <v>21425.200000000001</v>
+      <c r="D35" s="45">
+        <v>23483</v>
+      </c>
+      <c r="E35" s="37">
+        <v>31702</v>
+      </c>
+      <c r="F35" s="37">
+        <v>33795</v>
+      </c>
+      <c r="G35" s="37">
+        <v>38520</v>
+      </c>
+      <c r="H35" s="46">
+        <v>25406</v>
+      </c>
+      <c r="I35" s="47">
+        <f t="shared" si="0"/>
+        <v>30581.200000000001</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="18"/>
-      <c r="C36" s="41"/>
-      <c r="D36" s="32">
-        <v>46791391</v>
-      </c>
-      <c r="E36" s="19">
-        <v>41606051</v>
-      </c>
-      <c r="F36" s="19">
-        <v>47928001</v>
-      </c>
-      <c r="G36" s="19">
-        <v>39779875</v>
-      </c>
-      <c r="H36" s="24">
-        <v>39764980</v>
-      </c>
-      <c r="I36" s="28">
-        <f t="shared" si="0"/>
-        <v>43174059.600000001</v>
+      <c r="B36" s="15"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="28">
+        <v>37140883</v>
+      </c>
+      <c r="E36" s="16">
+        <v>39016457</v>
+      </c>
+      <c r="F36" s="16">
+        <v>38273955</v>
+      </c>
+      <c r="G36" s="16">
+        <v>40640198</v>
+      </c>
+      <c r="H36" s="20">
+        <v>37709528</v>
+      </c>
+      <c r="I36" s="24">
+        <f t="shared" si="0"/>
+        <v>38556204.200000003</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
+      <c r="B37" s="12"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A38" s="1"/>

--- a/Task3.xlsx
+++ b/Task3.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="17">
   <si>
     <t>Threads</t>
   </si>
@@ -71,10 +71,6 @@
   <si>
     <t xml:space="preserve">
 3223190</t>
-  </si>
-  <si>
-    <t>23765232
-23765232</t>
   </si>
 </sst>
 </file>
@@ -586,7 +582,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -611,7 +607,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -645,6 +640,9 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="33" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -661,9 +659,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -968,17 +967,17 @@
       <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="11"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="11"/>
+      <c r="F3" s="62"/>
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.35">
@@ -1004,13 +1003,13 @@
       </c>
     </row>
     <row r="7" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="24" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -1028,13 +1027,13 @@
       <c r="I7" s="22"/>
     </row>
     <row r="8" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="29">
+      <c r="B8" s="28">
         <v>2</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="25">
         <v>160</v>
       </c>
       <c r="E8" s="4">
@@ -1055,9 +1054,9 @@
       </c>
     </row>
     <row r="9" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="38"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="40">
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="39">
         <v>3013644</v>
       </c>
       <c r="E9" s="8">
@@ -1069,55 +1068,55 @@
       <c r="G9" s="8">
         <v>2425192</v>
       </c>
-      <c r="H9" s="64" t="s">
+      <c r="H9" s="57" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="41">
         <f t="shared" ref="I9:I36" si="0">AVERAGE(D9:H9)</f>
         <v>2856539</v>
       </c>
     </row>
     <row r="10" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="54"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
       <c r="I10" s="23"/>
     </row>
     <row r="11" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="43">
+      <c r="B11" s="42">
         <v>2</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="44">
         <v>129</v>
       </c>
-      <c r="E11" s="37">
+      <c r="E11" s="36">
         <v>119</v>
       </c>
-      <c r="F11" s="37">
+      <c r="F11" s="36">
         <v>123</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <v>119</v>
       </c>
-      <c r="H11" s="46">
+      <c r="H11" s="45">
         <v>175</v>
       </c>
-      <c r="I11" s="47">
+      <c r="I11" s="64">
         <f t="shared" si="0"/>
         <v>133</v>
       </c>
     </row>
     <row r="12" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="14"/>
-      <c r="C12" s="34"/>
-      <c r="D12" s="27">
+      <c r="C12" s="33"/>
+      <c r="D12" s="26">
         <v>2015928</v>
       </c>
       <c r="E12" s="3">
@@ -1132,29 +1131,29 @@
       <c r="H12" s="19">
         <v>2009653</v>
       </c>
-      <c r="I12" s="23">
+      <c r="I12" s="65">
         <f t="shared" si="0"/>
         <v>2017723.8</v>
       </c>
     </row>
     <row r="13" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="14"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="27"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="26"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="19"/>
-      <c r="I13" s="23"/>
+      <c r="I13" s="65"/>
     </row>
     <row r="14" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="13">
         <v>4</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <v>688</v>
       </c>
       <c r="E14" s="4">
@@ -1176,9 +1175,9 @@
       <c r="M14" s="12"/>
     </row>
     <row r="15" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40">
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39">
         <v>10724919</v>
       </c>
       <c r="E15" s="8">
@@ -1190,55 +1189,55 @@
       <c r="G15" s="8">
         <v>9274223</v>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="40">
         <v>8521116</v>
       </c>
-      <c r="I15" s="42">
+      <c r="I15" s="41">
         <f t="shared" si="0"/>
         <v>8656621</v>
       </c>
     </row>
     <row r="16" spans="2:13" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="54"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="36"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="36"/>
+      <c r="B16" s="53"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="35"/>
+      <c r="E16" s="35"/>
+      <c r="F16" s="35"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="35"/>
       <c r="I16" s="23"/>
     </row>
     <row r="17" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="43">
+      <c r="B17" s="42">
         <v>4</v>
       </c>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="44">
         <v>432</v>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="36">
         <v>470</v>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="36">
         <v>316</v>
       </c>
-      <c r="G17" s="37">
+      <c r="G17" s="36">
         <v>611</v>
       </c>
-      <c r="H17" s="46">
+      <c r="H17" s="45">
         <v>483</v>
       </c>
-      <c r="I17" s="47">
+      <c r="I17" s="64">
         <f t="shared" si="0"/>
         <v>462.4</v>
       </c>
     </row>
     <row r="18" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="48"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="50">
+      <c r="B18" s="47"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="49">
         <v>4288674</v>
       </c>
       <c r="E18" s="7">
@@ -1250,32 +1249,32 @@
       <c r="G18" s="7">
         <v>4268492</v>
       </c>
-      <c r="H18" s="51">
+      <c r="H18" s="50">
         <v>4202048</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="66">
         <f t="shared" si="0"/>
         <v>4217805.2</v>
       </c>
     </row>
     <row r="19" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="56"/>
-      <c r="C19" s="57"/>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="53"/>
-      <c r="H19" s="53"/>
-      <c r="I19" s="23"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="65"/>
     </row>
     <row r="20" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="29">
+      <c r="B20" s="28">
         <v>8</v>
       </c>
-      <c r="C20" s="32" t="s">
+      <c r="C20" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="51">
         <v>2280</v>
       </c>
       <c r="E20" s="10">
@@ -1290,15 +1289,15 @@
       <c r="H20" s="17">
         <v>2015</v>
       </c>
-      <c r="I20" s="47">
+      <c r="I20" s="46">
         <f t="shared" si="0"/>
         <v>2046.2</v>
       </c>
     </row>
     <row r="21" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="38"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="40">
+      <c r="B21" s="37"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="39">
         <v>29073011</v>
       </c>
       <c r="E21" s="8">
@@ -1310,55 +1309,55 @@
       <c r="G21" s="8">
         <v>23052519</v>
       </c>
-      <c r="H21" s="64" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="42">
-        <f t="shared" si="0"/>
-        <v>27450768.5</v>
+      <c r="H21" s="57">
+        <v>23765232</v>
+      </c>
+      <c r="I21" s="41">
+        <f t="shared" si="0"/>
+        <v>26713661.199999999</v>
       </c>
     </row>
     <row r="22" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="54"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
+      <c r="B22" s="53"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
       <c r="I22" s="23"/>
     </row>
     <row r="23" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="43">
+      <c r="B23" s="42">
         <v>8</v>
       </c>
-      <c r="C23" s="44" t="s">
+      <c r="C23" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D23" s="45">
+      <c r="D23" s="44">
         <v>1233</v>
       </c>
-      <c r="E23" s="37">
+      <c r="E23" s="36">
         <v>1500</v>
       </c>
-      <c r="F23" s="37">
+      <c r="F23" s="36">
         <v>2281</v>
       </c>
-      <c r="G23" s="37">
+      <c r="G23" s="36">
         <v>1822</v>
       </c>
-      <c r="H23" s="46">
+      <c r="H23" s="45">
         <v>2140</v>
       </c>
-      <c r="I23" s="47">
+      <c r="I23" s="64">
         <f t="shared" si="0"/>
         <v>1795.2</v>
       </c>
     </row>
     <row r="24" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="48"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="50">
+      <c r="B24" s="47"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="49">
         <v>8709783</v>
       </c>
       <c r="E24" s="7">
@@ -1370,32 +1369,32 @@
       <c r="G24" s="7">
         <v>10164954</v>
       </c>
-      <c r="H24" s="51">
+      <c r="H24" s="50">
         <v>9132874</v>
       </c>
-      <c r="I24" s="42">
+      <c r="I24" s="66">
         <f t="shared" si="0"/>
         <v>9132675.8000000007</v>
       </c>
     </row>
     <row r="25" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="56"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="53"/>
-      <c r="G25" s="53"/>
-      <c r="H25" s="53"/>
-      <c r="I25" s="23"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="52"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="52"/>
+      <c r="G25" s="52"/>
+      <c r="H25" s="52"/>
+      <c r="I25" s="65"/>
     </row>
     <row r="26" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="29">
+      <c r="B26" s="28">
         <v>16</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D26" s="52">
+      <c r="D26" s="51">
         <v>6054</v>
       </c>
       <c r="E26" s="10">
@@ -1410,15 +1409,15 @@
       <c r="H26" s="17">
         <v>6273</v>
       </c>
-      <c r="I26" s="47">
+      <c r="I26" s="46">
         <f t="shared" si="0"/>
         <v>6571</v>
       </c>
     </row>
     <row r="27" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="38"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="40">
+      <c r="B27" s="37"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="39">
         <v>74444287</v>
       </c>
       <c r="E27" s="8">
@@ -1430,55 +1429,55 @@
       <c r="G27" s="8">
         <v>97810478</v>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="40">
         <v>81107249</v>
       </c>
-      <c r="I27" s="42">
+      <c r="I27" s="41">
         <f t="shared" si="0"/>
         <v>96239672.200000003</v>
       </c>
     </row>
     <row r="28" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="54"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="36"/>
+      <c r="B28" s="53"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
       <c r="I28" s="23"/>
     </row>
     <row r="29" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="43">
+      <c r="B29" s="42">
         <v>16</v>
       </c>
-      <c r="C29" s="44" t="s">
+      <c r="C29" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D29" s="45">
+      <c r="D29" s="44">
         <v>5446</v>
       </c>
-      <c r="E29" s="37">
-        <v>5241</v>
-      </c>
-      <c r="F29" s="37">
+      <c r="E29" s="36">
+        <v>5141</v>
+      </c>
+      <c r="F29" s="36">
         <v>5410</v>
       </c>
-      <c r="G29" s="37">
+      <c r="G29" s="36">
         <v>6629</v>
       </c>
-      <c r="H29" s="46">
+      <c r="H29" s="45">
         <v>9822</v>
       </c>
-      <c r="I29" s="47">
-        <f t="shared" si="0"/>
-        <v>6509.6</v>
+      <c r="I29" s="64">
+        <f t="shared" si="0"/>
+        <v>6489.6</v>
       </c>
     </row>
     <row r="30" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="48"/>
-      <c r="C30" s="49"/>
-      <c r="D30" s="50">
+      <c r="B30" s="47"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="49">
         <v>19049520</v>
       </c>
       <c r="E30" s="7">
@@ -1490,32 +1489,32 @@
       <c r="G30" s="7">
         <v>19554301</v>
       </c>
-      <c r="H30" s="51">
+      <c r="H30" s="50">
         <v>22787666</v>
       </c>
-      <c r="I30" s="42">
+      <c r="I30" s="66">
         <f t="shared" si="0"/>
         <v>19739175.399999999</v>
       </c>
     </row>
     <row r="31" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="56"/>
-      <c r="C31" s="57"/>
-      <c r="D31" s="53"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="23"/>
+      <c r="B31" s="55"/>
+      <c r="C31" s="56"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="65"/>
     </row>
     <row r="32" spans="2:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="29">
+      <c r="B32" s="28">
         <v>32</v>
       </c>
-      <c r="C32" s="32" t="s">
+      <c r="C32" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D32" s="52">
+      <c r="D32" s="51">
         <v>21387</v>
       </c>
       <c r="E32" s="10">
@@ -1530,15 +1529,15 @@
       <c r="H32" s="17">
         <v>40206</v>
       </c>
-      <c r="I32" s="47">
+      <c r="I32" s="46">
         <f t="shared" si="0"/>
         <v>33423</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40">
+      <c r="B33" s="37"/>
+      <c r="C33" s="38"/>
+      <c r="D33" s="39">
         <v>374156605</v>
       </c>
       <c r="E33" s="8">
@@ -1550,55 +1549,55 @@
       <c r="G33" s="8">
         <v>358964408</v>
       </c>
-      <c r="H33" s="41">
+      <c r="H33" s="40">
         <v>360398381</v>
       </c>
-      <c r="I33" s="42">
+      <c r="I33" s="41">
         <f t="shared" si="0"/>
         <v>381121252</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="54"/>
-      <c r="C34" s="55"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="54"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
       <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="43">
+      <c r="B35" s="42">
         <v>32</v>
       </c>
-      <c r="C35" s="44" t="s">
+      <c r="C35" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="D35" s="45">
+      <c r="D35" s="44">
         <v>23483</v>
       </c>
-      <c r="E35" s="37">
+      <c r="E35" s="36">
         <v>31702</v>
       </c>
-      <c r="F35" s="37">
+      <c r="F35" s="36">
         <v>33795</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <v>38520</v>
       </c>
-      <c r="H35" s="46">
+      <c r="H35" s="45">
         <v>25406</v>
       </c>
-      <c r="I35" s="47">
+      <c r="I35" s="64">
         <f t="shared" si="0"/>
         <v>30581.200000000001</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="1" customFormat="1" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="15"/>
-      <c r="C36" s="35"/>
-      <c r="D36" s="28">
+      <c r="C36" s="34"/>
+      <c r="D36" s="27">
         <v>37140883</v>
       </c>
       <c r="E36" s="16">
@@ -1613,7 +1612,7 @@
       <c r="H36" s="20">
         <v>37709528</v>
       </c>
-      <c r="I36" s="24">
+      <c r="I36" s="67">
         <f t="shared" si="0"/>
         <v>38556204.200000003</v>
       </c>
@@ -1650,8 +1649,8 @@
   <mergeCells count="4">
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="B6:C6"/>
-    <mergeCell ref="E2:G2"/>
     <mergeCell ref="E4:G4"/>
+    <mergeCell ref="E3:F3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
